--- a/excel/read_dokho.xlsx
+++ b/excel/read_dokho.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\VISUAL\my-project\QuanLyQuiz\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F84C47C-8433-4109-942F-6950E7AE72B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F31B4E34-963B-4D4C-990E-BCD644E60F87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{3871BE9E-DE84-4E3E-AE7B-6CFB86CE809F}"/>
   </bookViews>
@@ -48,12 +48,19 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="14"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -76,8 +83,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -419,7 +427,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
